--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asael\Pictures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Betty\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB1CAA1A-5F83-4C8B-A8C9-219A5127C2BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{947ED52F-008B-4363-BE3E-35CCA397BF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2160" yWindow="2145" windowWidth="20295" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +269,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -557,14 +561,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,7 +603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -634,7 +638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -669,7 +673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -704,7 +708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -739,7 +743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -774,7 +778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -809,7 +813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -844,7 +848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -879,7 +883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -914,7 +918,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -949,7 +953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -984,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1019,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1054,7 +1058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1089,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -1124,7 +1128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1167,14 +1171,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1209,7 +1213,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1217,34 +1221,34 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1287,7 +1291,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -1302,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="4">
         <v>0</v>
@@ -1311,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="K4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1322,25 +1326,25 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D5" s="4">
         <v>0</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -1349,7 +1353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1384,7 +1388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1392,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4">
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -1419,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1454,7 +1458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1489,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1500,22 +1504,22 @@
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F10" s="4">
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -1524,7 +1528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1559,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1594,7 +1598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1629,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1664,7 +1668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1672,25 +1676,25 @@
         <v>38</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" s="4">
         <v>0</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="4">
         <v>0</v>
@@ -1699,7 +1703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -1710,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
@@ -1734,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1745,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>
@@ -1777,14 +1781,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1819,7 +1823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1854,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1889,7 +1893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1924,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1959,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1994,7 +1998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -2029,7 +2033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -2064,7 +2068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2099,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -2134,7 +2138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -2169,7 +2173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -2204,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -2239,7 +2243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -2274,7 +2278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -2309,7 +2313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -2344,7 +2348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -2387,14 +2391,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2429,7 +2433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -2464,7 +2468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2499,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2534,7 +2538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -2569,7 +2573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -2604,7 +2608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -2639,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -2674,7 +2678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2709,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -2744,7 +2748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,7 +2783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -2814,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -2849,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -2884,7 +2888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -2919,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -2954,7 +2958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Betty\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{947ED52F-008B-4363-BE3E-35CCA397BF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A9C80CC-EBF4-4B57-B916-953651F2D9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -1221,22 +1221,22 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4">
         <v>6</v>
       </c>
-      <c r="D2" s="4">
-        <v>4</v>
-      </c>
-      <c r="E2" s="4">
-        <v>4</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
       <c r="G2" s="4">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H2" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" s="4">
         <v>1</v>
@@ -1326,25 +1326,25 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>5</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
         <v>6</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>4</v>
       </c>
       <c r="J5" s="4">
         <v>0</v>
@@ -1373,7 +1373,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="4">
         <v>0</v>
@@ -1408,7 +1408,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" s="4">
         <v>0</v>
@@ -1507,22 +1507,22 @@
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H10" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I10" s="4">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="J10" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" s="4">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4">
         <v>0</v>
@@ -1676,13 +1676,13 @@
         <v>38</v>
       </c>
       <c r="C15" s="4">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
@@ -1694,10 +1694,10 @@
         <v>0</v>
       </c>
       <c r="I15" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J15" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" s="4">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Betty\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A9C80CC-EBF4-4B57-B916-953651F2D9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C286E9C-8D6B-47E6-BC99-874EA7845AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1221,31 +1221,31 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
       </c>
       <c r="G2" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H2" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I2" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K2" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1326,19 +1326,19 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>6</v>
       </c>
       <c r="J5" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -1507,19 +1507,19 @@
         <v>1</v>
       </c>
       <c r="E10" s="4">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
       </c>
       <c r="G10" s="4">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" s="4">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="J10" s="4">
         <v>2</v>
@@ -1571,7 +1571,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4">
         <v>0</v>
@@ -1676,28 +1676,28 @@
         <v>38</v>
       </c>
       <c r="C15" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D15" s="4">
         <v>3</v>
       </c>
       <c r="E15" s="4">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>6</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
         <v>7</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>3</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
-        <v>4</v>
-      </c>
       <c r="J15" s="4">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K15" s="4">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Betty\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C286E9C-8D6B-47E6-BC99-874EA7845AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{59C7C60E-DA28-45C4-93ED-3CD22E8B59B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -1221,10 +1221,10 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" s="4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" s="4">
         <v>9</v>
@@ -1233,19 +1233,19 @@
         <v>6</v>
       </c>
       <c r="G2" s="4">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H2" s="4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I2" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J2" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K2" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -1303,7 +1303,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="4">
         <v>1</v>
@@ -1326,28 +1326,28 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4">
         <v>1</v>
       </c>
       <c r="E5" s="4">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
+        <v>7</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4">
+        <v>11</v>
+      </c>
+      <c r="J5" s="4">
         <v>4</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>6</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
-        <v>6</v>
-      </c>
-      <c r="J5" s="4">
-        <v>2</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -1396,10 +1396,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="4">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4">
         <v>1</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
@@ -1504,16 +1504,16 @@
         <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10" s="4">
         <v>1</v>
       </c>
       <c r="G10" s="4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" s="4">
         <v>5</v>
@@ -1571,25 +1571,25 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
+        <v>2</v>
+      </c>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
         <v>1</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0</v>
       </c>
       <c r="J12" s="4">
         <v>1</v>
@@ -1676,28 +1676,28 @@
         <v>38</v>
       </c>
       <c r="C15" s="4">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D15" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H15" s="4">
         <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K15" s="4">
         <v>0</v>
@@ -1749,7 +1749,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="4">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Betty\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59C7C60E-DA28-45C4-93ED-3CD22E8B59B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E613CAB4-3D12-4088-94AC-DE642DBA3AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1221,25 +1221,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D2" s="4">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E2" s="4">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4">
         <v>6</v>
       </c>
       <c r="G2" s="4">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="H2" s="4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I2" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4">
         <v>14</v>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4">
         <v>1</v>
@@ -1326,25 +1326,25 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H5" s="4">
         <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J5" s="4">
         <v>4</v>
@@ -1396,10 +1396,10 @@
         <v>22</v>
       </c>
       <c r="C7" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4">
         <v>1</v>
@@ -1434,10 +1434,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4">
         <v>0</v>
@@ -1446,13 +1446,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
       </c>
       <c r="J8" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K8" s="4">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>28</v>
       </c>
       <c r="C10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4">
         <v>13</v>
@@ -1519,10 +1519,10 @@
         <v>5</v>
       </c>
       <c r="I10" s="4">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J10" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="4">
         <v>0</v>
@@ -1571,13 +1571,13 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4">
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
@@ -1676,10 +1676,10 @@
         <v>38</v>
       </c>
       <c r="C15" s="4">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D15" s="4">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E15" s="4">
         <v>16</v>
@@ -1688,16 +1688,16 @@
         <v>0</v>
       </c>
       <c r="G15" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H15" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I15" s="4">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K15" s="4">
         <v>0</v>
@@ -1711,13 +1711,13 @@
         <v>40</v>
       </c>
       <c r="C16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
       </c>
       <c r="E16" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>42</v>
       </c>
       <c r="C17" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D17" s="4">
         <v>5</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Betty\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E613CAB4-3D12-4088-94AC-DE642DBA3AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63064212-45C0-4E40-9B2A-CBF9A8B57EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,22 +186,34 @@
       <sz val="9"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -244,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -254,6 +266,7 @@
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1170,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
@@ -1738,7 +1751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1772,6 +1785,9 @@
       <c r="K17" s="4">
         <v>0</v>
       </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q19" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1831,25 +1847,25 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D2" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="4">
         <v>0</v>
       </c>
       <c r="G2" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" s="4">
         <v>0</v>
       </c>
       <c r="I2" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" s="4">
         <v>0</v>
@@ -1936,13 +1952,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -1954,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -2012,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -2123,13 +2139,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -2187,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
@@ -2286,13 +2302,13 @@
         <v>38</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
@@ -2301,16 +2317,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2374,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Betty\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63064212-45C0-4E40-9B2A-CBF9A8B57EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B77F2D61-E98C-4661-A751-54D7BFF2CC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -186,26 +186,22 @@
       <sz val="9"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -256,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -267,6 +263,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -282,10 +281,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,14 +569,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,7 +611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -651,7 +646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -686,7 +681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -721,7 +716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -756,7 +751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -791,7 +786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -826,7 +821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -861,7 +856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -896,7 +891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -931,7 +926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -966,7 +961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1001,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1036,7 +1031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1071,7 +1066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1106,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -1141,7 +1136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1184,14 +1179,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1226,7 +1221,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1261,7 +1256,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1296,7 +1291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -1331,7 +1326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -1366,7 +1361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -1401,7 +1396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -1436,7 +1431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1471,7 +1466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -1506,7 +1501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -1541,7 +1536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -1576,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -1611,7 +1606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -1646,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -1681,7 +1676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -1716,7 +1711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -1751,7 +1746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
@@ -1786,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="Q19" s="5"/>
     </row>
   </sheetData>
@@ -1797,14 +1792,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1839,563 +1834,563 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="6">
+        <v>6</v>
+      </c>
+      <c r="D2" s="6">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6">
         <v>5</v>
       </c>
-      <c r="D2" s="4">
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6">
+        <v>6</v>
+      </c>
+      <c r="H2" s="6">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6">
+        <v>3</v>
+      </c>
+      <c r="J2" s="6">
+        <v>6</v>
+      </c>
+      <c r="K2" s="6">
         <v>2</v>
       </c>
-      <c r="E2" s="4">
-        <v>2</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4">
-        <v>3</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>2</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0</v>
-      </c>
-      <c r="I3" s="4">
-        <v>0</v>
-      </c>
-      <c r="J3" s="4">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C3" s="6">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0</v>
+      </c>
+      <c r="K3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0</v>
-      </c>
-      <c r="H4" s="4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C4" s="6">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6">
+        <v>4</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6">
+        <v>0</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0</v>
+      </c>
+      <c r="K4" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <v>3</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0</v>
-      </c>
-      <c r="H5" s="4">
-        <v>0</v>
-      </c>
-      <c r="I5" s="4">
+      <c r="C5" s="6">
+        <v>4</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6">
+        <v>1</v>
+      </c>
+      <c r="I5" s="6">
+        <v>2</v>
+      </c>
+      <c r="J5" s="6">
         <v>5</v>
       </c>
-      <c r="J5" s="4">
-        <v>3</v>
-      </c>
-      <c r="K5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="K5" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="4">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
-      <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>0</v>
+      </c>
+      <c r="I7" s="6">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-      <c r="H8" s="4">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4">
-        <v>0</v>
-      </c>
-      <c r="K8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4">
-        <v>0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4">
-        <v>0</v>
-      </c>
-      <c r="K9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C9" s="6">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0</v>
+      </c>
+      <c r="G10" s="6">
         <v>3</v>
       </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
-        <v>20</v>
-      </c>
-      <c r="J10" s="4">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H10" s="6">
+        <v>0</v>
+      </c>
+      <c r="I10" s="6">
+        <v>25</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0</v>
+      </c>
+      <c r="K10" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="4">
-        <v>0</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C11" s="6">
+        <v>0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="4">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C12" s="6">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="4">
-        <v>0</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4">
-        <v>0</v>
-      </c>
-      <c r="K13" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C13" s="6">
+        <v>0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6">
+        <v>0</v>
+      </c>
+      <c r="K13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="4">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4">
-        <v>0</v>
-      </c>
-      <c r="E14" s="4">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4">
-        <v>0</v>
-      </c>
-      <c r="K14" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C14" s="6">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="4">
-        <v>3</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
-        <v>3</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4">
+      <c r="C15" s="6">
         <v>5</v>
       </c>
-      <c r="J15" s="4">
+      <c r="D15" s="6">
+        <v>6</v>
+      </c>
+      <c r="E15" s="6">
+        <v>7</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0</v>
+      </c>
+      <c r="G15" s="6">
+        <v>1</v>
+      </c>
+      <c r="H15" s="6">
         <v>2</v>
       </c>
-      <c r="K15" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="I15" s="6">
+        <v>8</v>
+      </c>
+      <c r="J15" s="6">
+        <v>4</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4">
-        <v>0</v>
-      </c>
-      <c r="I16" s="4">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4">
-        <v>0</v>
-      </c>
-      <c r="K16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="C16" s="6">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0</v>
+      </c>
+      <c r="K16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="4">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4">
-        <v>0</v>
-      </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0</v>
-      </c>
-      <c r="H17" s="4">
-        <v>0</v>
-      </c>
-      <c r="I17" s="4">
-        <v>1</v>
-      </c>
-      <c r="J17" s="4">
-        <v>0</v>
-      </c>
-      <c r="K17" s="4">
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>0</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1</v>
+      </c>
+      <c r="J17" s="6">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2407,14 +2402,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2449,7 +2444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -2484,7 +2479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -2519,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2554,7 +2549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -2589,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -2624,7 +2619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -2659,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -2694,7 +2689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -2729,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
@@ -2764,7 +2759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
@@ -2799,7 +2794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -2834,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
@@ -2869,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>35</v>
       </c>
@@ -2904,7 +2899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>37</v>
       </c>
@@ -2939,7 +2934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
@@ -2974,7 +2969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>41</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B77F2D61-E98C-4661-A751-54D7BFF2CC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3371AE99-BCED-4D2A-80B6-CFE959CBA8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,7 +573,9 @@
   <cols>
     <col min="1" max="1" width="22" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="11" width="14" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="9.1796875" customWidth="1"/>
+    <col min="10" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -1842,31 +1844,31 @@
         <v>12</v>
       </c>
       <c r="C2" s="6">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6">
         <v>6</v>
       </c>
-      <c r="D2" s="6">
-        <v>3</v>
-      </c>
       <c r="E2" s="6">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6">
+        <v>8</v>
+      </c>
+      <c r="H2" s="6">
+        <v>4</v>
+      </c>
+      <c r="I2" s="6">
         <v>5</v>
-      </c>
-      <c r="F2" s="6">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6">
-        <v>6</v>
-      </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6">
-        <v>3</v>
       </c>
       <c r="J2" s="6">
         <v>6</v>
       </c>
       <c r="K2" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -1912,7 +1914,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -1933,7 +1935,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="6">
         <v>0</v>
@@ -1947,25 +1949,25 @@
         <v>18</v>
       </c>
       <c r="C5" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
       </c>
       <c r="G5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J5" s="6">
         <v>5</v>
@@ -2073,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
@@ -2140,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J10" s="6">
         <v>0</v>
@@ -2262,7 +2264,7 @@
         <v>36</v>
       </c>
       <c r="C14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6">
         <v>0</v>
@@ -2280,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" s="6">
         <v>0</v>
@@ -2297,25 +2299,25 @@
         <v>38</v>
       </c>
       <c r="C15" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D15" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="6">
         <v>0</v>
       </c>
       <c r="G15" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I15" s="6">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J15" s="6">
         <v>4</v>
@@ -2367,10 +2369,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
@@ -2388,7 +2390,7 @@
         <v>1</v>
       </c>
       <c r="J17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="6">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3371AE99-BCED-4D2A-80B6-CFE959CBA8B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{387620E0-D206-4E7C-BC97-252181AC6F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1844,22 +1844,22 @@
         <v>12</v>
       </c>
       <c r="C2" s="6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D2" s="6">
         <v>6</v>
       </c>
       <c r="E2" s="6">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F2" s="6">
         <v>1</v>
       </c>
       <c r="G2" s="6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H2" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I2" s="6">
         <v>5</v>
@@ -1914,7 +1914,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -1949,31 +1949,31 @@
         <v>18</v>
       </c>
       <c r="C5" s="6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
       </c>
       <c r="G5" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5" s="6">
         <v>2</v>
       </c>
       <c r="I5" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J5" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6">
         <v>0</v>
@@ -2072,7 +2072,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="6">
         <v>1</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" s="6">
         <v>0</v>
@@ -2194,10 +2194,10 @@
         <v>32</v>
       </c>
       <c r="C12" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="6">
         <v>0</v>
@@ -2299,7 +2299,7 @@
         <v>38</v>
       </c>
       <c r="C15" s="6">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6">
         <v>7</v>
@@ -2317,7 +2317,7 @@
         <v>3</v>
       </c>
       <c r="I15" s="6">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J15" s="6">
         <v>4</v>
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J17" s="6">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{387620E0-D206-4E7C-BC97-252181AC6F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46033E1D-8A8D-4A84-97A6-FC4CF575926B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -281,6 +281,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1844,19 +1848,19 @@
         <v>12</v>
       </c>
       <c r="C2" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F2" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H2" s="6">
         <v>5</v>
@@ -1865,7 +1869,7 @@
         <v>5</v>
       </c>
       <c r="J2" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K2" s="6">
         <v>7</v>
@@ -1914,7 +1918,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -1949,10 +1953,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" s="6">
         <v>10</v>
@@ -1961,13 +1965,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="6">
         <v>2</v>
       </c>
       <c r="I5" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="6">
         <v>6</v>
@@ -2136,13 +2140,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H10" s="6">
         <v>0</v>
       </c>
       <c r="I10" s="6">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J10" s="6">
         <v>0</v>
@@ -2299,28 +2303,28 @@
         <v>38</v>
       </c>
       <c r="C15" s="6">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D15" s="6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E15" s="6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F15" s="6">
         <v>0</v>
       </c>
       <c r="G15" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I15" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J15" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="6">
         <v>1</v>
@@ -2387,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J17" s="6">
         <v>1</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46033E1D-8A8D-4A84-97A6-FC4CF575926B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DD49765-54DA-4AD9-B09C-8F6C0BC38173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -186,22 +186,26 @@
       <sz val="9"/>
       <color rgb="FF888888"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -281,10 +285,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2061,7 +2061,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="6">
         <v>0</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="6">
         <v>1</v>
@@ -2458,31 +2458,31 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -2528,13 +2528,13 @@
         <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
       </c>
       <c r="E4" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4">
         <v>0</v>
@@ -2563,13 +2563,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -2578,13 +2578,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -2808,7 +2808,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="4">
         <v>0</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="4">
         <v>0</v>
@@ -2916,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -2928,13 +2928,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="4">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DD49765-54DA-4AD9-B09C-8F6C0BC38173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFC7155-F63C-4609-95FB-058F3A70EA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -256,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -267,9 +267,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1847,31 +1844,31 @@
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="4">
         <v>17</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="4">
         <v>10</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="4">
         <v>17</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>3</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="4">
         <v>18</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <v>5</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="4">
         <v>5</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
         <v>8</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>7</v>
       </c>
     </row>
@@ -1882,31 +1879,31 @@
       <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6">
-        <v>0</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0</v>
-      </c>
-      <c r="J3" s="6">
-        <v>0</v>
-      </c>
-      <c r="K3" s="6">
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1917,31 +1914,31 @@
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="4">
         <v>5</v>
       </c>
-      <c r="D4" s="6">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
-      </c>
-      <c r="G4" s="6">
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
         <v>4</v>
       </c>
-      <c r="H4" s="6">
-        <v>0</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>1</v>
-      </c>
-      <c r="K4" s="6">
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1952,31 +1949,31 @@
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="4">
         <v>10</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="4">
         <v>8</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="4">
         <v>10</v>
       </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5" s="4">
         <v>5</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <v>2</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="4">
         <v>13</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="4">
         <v>6</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="4">
         <v>1</v>
       </c>
     </row>
@@ -1987,31 +1984,31 @@
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="6">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
-      </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6">
-        <v>0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
+      <c r="C6" s="4">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2022,31 +2019,31 @@
       <c r="B7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="6">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
+      <c r="J7" s="4">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2057,31 +2054,31 @@
       <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="4">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
         <v>2</v>
       </c>
-      <c r="E8" s="6">
-        <v>0</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6">
+      <c r="E8" s="4">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
         <v>2</v>
       </c>
-      <c r="J8" s="6">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6">
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2092,31 +2089,31 @@
       <c r="B9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
+      <c r="C9" s="4">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2127,31 +2124,31 @@
       <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="6">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0</v>
-      </c>
-      <c r="F10" s="6">
-        <v>0</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="C10" s="4">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
         <v>5</v>
       </c>
-      <c r="H10" s="6">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6">
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
         <v>30</v>
       </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
+      <c r="J10" s="4">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2162,31 +2159,31 @@
       <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="6">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6">
+      <c r="C11" s="4">
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2197,31 +2194,31 @@
       <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="4">
         <v>2</v>
       </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6">
-        <v>0</v>
-      </c>
-      <c r="J12" s="6">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6">
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2232,31 +2229,31 @@
       <c r="B13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="6">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6">
-        <v>0</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6">
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2267,31 +2264,31 @@
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6">
-        <v>1</v>
-      </c>
-      <c r="J14" s="6">
-        <v>0</v>
-      </c>
-      <c r="K14" s="6">
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2302,31 +2299,31 @@
       <c r="B15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="4">
         <v>24</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="4">
         <v>13</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="4">
         <v>13</v>
       </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
         <v>4</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <v>5</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="4">
         <v>22</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="4">
         <v>5</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="4">
         <v>1</v>
       </c>
     </row>
@@ -2337,31 +2334,31 @@
       <c r="B16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="6">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0</v>
-      </c>
-      <c r="J16" s="6">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6">
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
         <v>0</v>
       </c>
     </row>
@@ -2372,31 +2369,31 @@
       <c r="B17" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="6">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6">
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
         <v>6</v>
       </c>
-      <c r="J17" s="6">
-        <v>1</v>
-      </c>
-      <c r="K17" s="6">
+      <c r="J17" s="4">
+        <v>1</v>
+      </c>
+      <c r="K17" s="4">
         <v>0</v>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFC7155-F63C-4609-95FB-058F3A70EA55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE7C9E30-36EB-44BF-B252-7C10A7649C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="1" r:id="rId1"/>
@@ -282,6 +282,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2455,31 +2459,31 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
+        <v>14</v>
+      </c>
+      <c r="D2" s="4">
         <v>8</v>
       </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
       <c r="E2" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F2" s="4">
         <v>4</v>
       </c>
       <c r="G2" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H2" s="4">
         <v>3</v>
       </c>
       <c r="I2" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2" s="4">
         <v>1</v>
       </c>
       <c r="K2" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -2560,10 +2564,10 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4">
         <v>5</v>
@@ -2572,16 +2576,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4">
+        <v>6</v>
+      </c>
+      <c r="J5" s="4">
         <v>5</v>
-      </c>
-      <c r="J5" s="4">
-        <v>3</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -2598,7 +2602,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -2633,10 +2637,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -2683,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -2747,13 +2751,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -2913,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4">
         <v>0</v>
@@ -2928,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J15" s="4">
         <v>1</v>
@@ -2980,7 +2984,7 @@
         <v>42</v>
       </c>
       <c r="C17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="4">
         <v>0</v>
@@ -2998,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="4">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FernandoMejia\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE7C9E30-36EB-44BF-B252-7C10A7649C0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C3D5AFC3-E9D0-49B0-9D09-EB8CD05302F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2459,31 +2459,31 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D2" s="4">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4">
+        <v>5</v>
+      </c>
+      <c r="G2" s="4">
+        <v>16</v>
+      </c>
+      <c r="H2" s="4">
+        <v>4</v>
+      </c>
+      <c r="I2" s="4">
+        <v>7</v>
+      </c>
+      <c r="J2" s="4">
+        <v>2</v>
+      </c>
+      <c r="K2" s="4">
         <v>8</v>
-      </c>
-      <c r="E2" s="4">
-        <v>10</v>
-      </c>
-      <c r="F2" s="4">
-        <v>4</v>
-      </c>
-      <c r="G2" s="4">
-        <v>9</v>
-      </c>
-      <c r="H2" s="4">
-        <v>3</v>
-      </c>
-      <c r="I2" s="4">
-        <v>4</v>
-      </c>
-      <c r="J2" s="4">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4">
-        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -2529,7 +2529,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4">
         <v>0</v>
@@ -2564,28 +2564,28 @@
         <v>18</v>
       </c>
       <c r="C5" s="4">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" s="4">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4">
         <v>7</v>
       </c>
-      <c r="E5" s="4">
-        <v>5</v>
-      </c>
       <c r="F5" s="4">
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4">
+        <v>23</v>
+      </c>
+      <c r="J5" s="4">
         <v>6</v>
-      </c>
-      <c r="J5" s="4">
-        <v>5</v>
       </c>
       <c r="K5" s="4">
         <v>0</v>
@@ -2634,13 +2634,13 @@
         <v>22</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="4">
         <v>0</v>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" s="4">
         <v>0</v>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="4">
         <v>0</v>
@@ -2748,7 +2748,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4">
         <v>1</v>
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J10" s="4">
         <v>0</v>
@@ -2812,16 +2812,16 @@
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
       </c>
       <c r="G12" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="4">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
@@ -2914,25 +2914,25 @@
         <v>38</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4">
+        <v>5</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
         <v>3</v>
       </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
       <c r="H15" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4">
         <v>1</v>
@@ -2987,10 +2987,10 @@
         <v>1</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
